--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3610"/>
+  <dimension ref="A1:E3611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97886,6 +97886,33 @@
         </is>
       </c>
     </row>
+    <row r="3611">
+      <c r="A3611" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B3611" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3611" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D3611" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E3611" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3611"/>
+  <dimension ref="A1:E3612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97913,6 +97913,33 @@
         </is>
       </c>
     </row>
+    <row r="3612">
+      <c r="A3612" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B3612" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3612" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3612" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E3612" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3612"/>
+  <dimension ref="A1:E3613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97940,6 +97940,33 @@
         </is>
       </c>
     </row>
+    <row r="3613">
+      <c r="A3613" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B3613" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3613" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D3613" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3613" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3613"/>
+  <dimension ref="A1:E3614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97967,6 +97967,33 @@
         </is>
       </c>
     </row>
+    <row r="3614">
+      <c r="A3614" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B3614" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3614" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D3614" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3614" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3614"/>
+  <dimension ref="A1:E3615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97994,6 +97994,33 @@
         </is>
       </c>
     </row>
+    <row r="3615">
+      <c r="A3615" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B3615" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3615" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3615" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3615" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3615"/>
+  <dimension ref="A1:E3616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98021,6 +98021,33 @@
         </is>
       </c>
     </row>
+    <row r="3616">
+      <c r="A3616" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B3616" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3616" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3616" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3616" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3616"/>
+  <dimension ref="A1:E3618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98048,6 +98048,60 @@
         </is>
       </c>
     </row>
+    <row r="3617">
+      <c r="A3617" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B3617" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3617" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D3617" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3617" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="3618">
+      <c r="A3618" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B3618" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3618" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3618" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E3618" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3618"/>
+  <dimension ref="A1:E3619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98102,6 +98102,33 @@
         </is>
       </c>
     </row>
+    <row r="3619">
+      <c r="A3619" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B3619" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3619" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D3619" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E3619" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3619"/>
+  <dimension ref="A1:E3620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98129,6 +98129,33 @@
         </is>
       </c>
     </row>
+    <row r="3620">
+      <c r="A3620" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B3620" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3620" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3620" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3620" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3620"/>
+  <dimension ref="A1:E3621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98156,6 +98156,33 @@
         </is>
       </c>
     </row>
+    <row r="3621">
+      <c r="A3621" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B3621" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3621" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3621" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E3621" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3621"/>
+  <dimension ref="A1:E3622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98183,6 +98183,33 @@
         </is>
       </c>
     </row>
+    <row r="3622">
+      <c r="A3622" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B3622" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3622" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D3622" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E3622" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3622"/>
+  <dimension ref="A1:E3623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98210,6 +98210,33 @@
         </is>
       </c>
     </row>
+    <row r="3623">
+      <c r="A3623" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B3623" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3623" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D3623" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E3623" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3623"/>
+  <dimension ref="A1:E3624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98237,6 +98237,33 @@
         </is>
       </c>
     </row>
+    <row r="3624">
+      <c r="A3624" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B3624" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3624" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D3624" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3624" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3624"/>
+  <dimension ref="A1:E3625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98264,6 +98264,33 @@
         </is>
       </c>
     </row>
+    <row r="3625">
+      <c r="A3625" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B3625" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3625" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3625" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3625" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3625"/>
+  <dimension ref="A1:E3626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98291,6 +98291,33 @@
         </is>
       </c>
     </row>
+    <row r="3626">
+      <c r="A3626" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B3626" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3626" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D3626" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3626" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3626"/>
+  <dimension ref="A1:E3627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98318,6 +98318,33 @@
         </is>
       </c>
     </row>
+    <row r="3627">
+      <c r="A3627" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B3627" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3627" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3627" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3627" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3627"/>
+  <dimension ref="A1:E3628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98345,6 +98345,33 @@
         </is>
       </c>
     </row>
+    <row r="3628">
+      <c r="A3628" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B3628" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3628" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D3628" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3628" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3628"/>
+  <dimension ref="A1:E3629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98372,6 +98372,33 @@
         </is>
       </c>
     </row>
+    <row r="3629">
+      <c r="A3629" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B3629" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3629" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D3629" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E3629" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3629"/>
+  <dimension ref="A1:E3630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98399,6 +98399,33 @@
         </is>
       </c>
     </row>
+    <row r="3630">
+      <c r="A3630" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B3630" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3630" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D3630" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E3630" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3630"/>
+  <dimension ref="A1:E3631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98426,6 +98426,33 @@
         </is>
       </c>
     </row>
+    <row r="3631">
+      <c r="A3631" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B3631" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3631" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3631" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E3631" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3631"/>
+  <dimension ref="A1:E3632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98453,6 +98453,33 @@
         </is>
       </c>
     </row>
+    <row r="3632">
+      <c r="A3632" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B3632" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3632" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D3632" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3632" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3632"/>
+  <dimension ref="A1:E3633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98480,6 +98480,33 @@
         </is>
       </c>
     </row>
+    <row r="3633">
+      <c r="A3633" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B3633" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3633" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3633" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E3633" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3633"/>
+  <dimension ref="A1:E3634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98507,6 +98507,33 @@
         </is>
       </c>
     </row>
+    <row r="3634">
+      <c r="A3634" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B3634" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3634" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3634" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3634" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3634"/>
+  <dimension ref="A1:E3635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98534,6 +98534,33 @@
         </is>
       </c>
     </row>
+    <row r="3635">
+      <c r="A3635" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B3635" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3635" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3635" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3635" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3635"/>
+  <dimension ref="A1:E3636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98561,6 +98561,33 @@
         </is>
       </c>
     </row>
+    <row r="3636">
+      <c r="A3636" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B3636" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3636" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3636" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3636" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3636"/>
+  <dimension ref="A1:E3637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98588,6 +98588,33 @@
         </is>
       </c>
     </row>
+    <row r="3637">
+      <c r="A3637" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B3637" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3637" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3637" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E3637" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3637"/>
+  <dimension ref="A1:E3638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98615,6 +98615,33 @@
         </is>
       </c>
     </row>
+    <row r="3638">
+      <c r="A3638" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B3638" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3638" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D3638" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3638" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3638"/>
+  <dimension ref="A1:E3639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98642,6 +98642,33 @@
         </is>
       </c>
     </row>
+    <row r="3639">
+      <c r="A3639" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B3639" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3639" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D3639" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3639" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3639"/>
+  <dimension ref="A1:E3640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98669,6 +98669,33 @@
         </is>
       </c>
     </row>
+    <row r="3640">
+      <c r="A3640" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B3640" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3640" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3640" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3640" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3640"/>
+  <dimension ref="A1:E3641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98696,6 +98696,33 @@
         </is>
       </c>
     </row>
+    <row r="3641">
+      <c r="A3641" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B3641" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3641" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3641" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3641" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3641"/>
+  <dimension ref="A1:E3642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98723,6 +98723,33 @@
         </is>
       </c>
     </row>
+    <row r="3642">
+      <c r="A3642" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B3642" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3642" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D3642" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3642" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3642"/>
+  <dimension ref="A1:E3643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98750,6 +98750,33 @@
         </is>
       </c>
     </row>
+    <row r="3643">
+      <c r="A3643" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B3643" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3643" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D3643" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3643" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3643"/>
+  <dimension ref="A1:E3644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98777,6 +98777,33 @@
         </is>
       </c>
     </row>
+    <row r="3644">
+      <c r="A3644" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B3644" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3644" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3644" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3644" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3644"/>
+  <dimension ref="A1:E3645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98804,6 +98804,33 @@
         </is>
       </c>
     </row>
+    <row r="3645">
+      <c r="A3645" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B3645" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3645" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3645" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3645" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3645"/>
+  <dimension ref="A1:E3646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98831,6 +98831,33 @@
         </is>
       </c>
     </row>
+    <row r="3646">
+      <c r="A3646" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B3646" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3646" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3646" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3646" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3646"/>
+  <dimension ref="A1:E3647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98858,6 +98858,33 @@
         </is>
       </c>
     </row>
+    <row r="3647">
+      <c r="A3647" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B3647" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3647" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D3647" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3647" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3647"/>
+  <dimension ref="A1:E3648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98885,6 +98885,33 @@
         </is>
       </c>
     </row>
+    <row r="3648">
+      <c r="A3648" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B3648" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3648" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3648" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E3648" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3648"/>
+  <dimension ref="A1:E3649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98912,6 +98912,33 @@
         </is>
       </c>
     </row>
+    <row r="3649">
+      <c r="A3649" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B3649" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3649" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D3649" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E3649" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3649"/>
+  <dimension ref="A1:E3650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98939,6 +98939,33 @@
         </is>
       </c>
     </row>
+    <row r="3650">
+      <c r="A3650" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B3650" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3650" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3650" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3650" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3650"/>
+  <dimension ref="A1:E3651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98966,6 +98966,33 @@
         </is>
       </c>
     </row>
+    <row r="3651">
+      <c r="A3651" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B3651" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3651" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3651" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3651" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3651"/>
+  <dimension ref="A1:E3652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98993,6 +98993,33 @@
         </is>
       </c>
     </row>
+    <row r="3652">
+      <c r="A3652" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B3652" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3652" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3652" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E3652" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3652"/>
+  <dimension ref="A1:E3653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99020,6 +99020,33 @@
         </is>
       </c>
     </row>
+    <row r="3653">
+      <c r="A3653" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B3653" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3653" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D3653" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3653" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3653"/>
+  <dimension ref="A1:E3654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99047,6 +99047,33 @@
         </is>
       </c>
     </row>
+    <row r="3654">
+      <c r="A3654" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B3654" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3654" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3654" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3654" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3654"/>
+  <dimension ref="A1:E3655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99074,6 +99074,33 @@
         </is>
       </c>
     </row>
+    <row r="3655">
+      <c r="A3655" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B3655" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3655" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D3655" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3655" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3655"/>
+  <dimension ref="A1:E3656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99101,6 +99101,33 @@
         </is>
       </c>
     </row>
+    <row r="3656">
+      <c r="A3656" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B3656" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3656" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3656" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3656" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3656"/>
+  <dimension ref="A1:E3657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99128,6 +99128,33 @@
         </is>
       </c>
     </row>
+    <row r="3657">
+      <c r="A3657" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B3657" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3657" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3657" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E3657" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3657"/>
+  <dimension ref="A1:E3658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99155,6 +99155,33 @@
         </is>
       </c>
     </row>
+    <row r="3658">
+      <c r="A3658" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B3658" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3658" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D3658" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3658" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3658"/>
+  <dimension ref="A1:E3659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99182,6 +99182,33 @@
         </is>
       </c>
     </row>
+    <row r="3659">
+      <c r="A3659" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B3659" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3659" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3659" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3659" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3659"/>
+  <dimension ref="A1:E3660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99209,6 +99209,33 @@
         </is>
       </c>
     </row>
+    <row r="3660">
+      <c r="A3660" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B3660" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3660" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D3660" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E3660" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3660"/>
+  <dimension ref="A1:E3661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99236,6 +99236,33 @@
         </is>
       </c>
     </row>
+    <row r="3661">
+      <c r="A3661" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B3661" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3661" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D3661" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3661" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3661"/>
+  <dimension ref="A1:E3662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99263,6 +99263,33 @@
         </is>
       </c>
     </row>
+    <row r="3662">
+      <c r="A3662" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B3662" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3662" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3662" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E3662" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3662"/>
+  <dimension ref="A1:E3663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99290,6 +99290,33 @@
         </is>
       </c>
     </row>
+    <row r="3663">
+      <c r="A3663" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B3663" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3663" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D3663" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E3663" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3663"/>
+  <dimension ref="A1:E3664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99317,6 +99317,33 @@
         </is>
       </c>
     </row>
+    <row r="3664">
+      <c r="A3664" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B3664" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3664" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D3664" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3664" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3664"/>
+  <dimension ref="A1:E3665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99344,6 +99344,33 @@
         </is>
       </c>
     </row>
+    <row r="3665">
+      <c r="A3665" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B3665" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3665" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D3665" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3665" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3665"/>
+  <dimension ref="A1:E3666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99371,6 +99371,33 @@
         </is>
       </c>
     </row>
+    <row r="3666">
+      <c r="A3666" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B3666" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3666" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D3666" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3666" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3666"/>
+  <dimension ref="A1:E3667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99398,6 +99398,33 @@
         </is>
       </c>
     </row>
+    <row r="3667">
+      <c r="A3667" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B3667" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3667" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D3667" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3667" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3667"/>
+  <dimension ref="A1:E3668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99425,6 +99425,33 @@
         </is>
       </c>
     </row>
+    <row r="3668">
+      <c r="A3668" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B3668" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3668" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D3668" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3668" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3668"/>
+  <dimension ref="A1:E3669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99452,6 +99452,33 @@
         </is>
       </c>
     </row>
+    <row r="3669">
+      <c r="A3669" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3669" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3669" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3669" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3669" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3669"/>
+  <dimension ref="A1:E3670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99479,6 +99479,33 @@
         </is>
       </c>
     </row>
+    <row r="3670">
+      <c r="A3670" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3670" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3670" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3670" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3670" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3670"/>
+  <dimension ref="A1:E3671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99506,6 +99506,33 @@
         </is>
       </c>
     </row>
+    <row r="3671">
+      <c r="A3671" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B3671" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3671" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3671" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E3671" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3671"/>
+  <dimension ref="A1:E3672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99533,6 +99533,33 @@
         </is>
       </c>
     </row>
+    <row r="3672">
+      <c r="A3672" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B3672" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3672" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3672" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3672" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3672"/>
+  <dimension ref="A1:E3673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99560,6 +99560,33 @@
         </is>
       </c>
     </row>
+    <row r="3673">
+      <c r="A3673" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B3673" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3673" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D3673" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3673" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3673"/>
+  <dimension ref="A1:E3674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99587,6 +99587,33 @@
         </is>
       </c>
     </row>
+    <row r="3674">
+      <c r="A3674" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B3674" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3674" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D3674" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E3674" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3674"/>
+  <dimension ref="A1:E3675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99614,6 +99614,33 @@
         </is>
       </c>
     </row>
+    <row r="3675">
+      <c r="A3675" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B3675" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3675" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3675" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3675" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3675"/>
+  <dimension ref="A1:E3676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99641,6 +99641,33 @@
         </is>
       </c>
     </row>
+    <row r="3676">
+      <c r="A3676" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B3676" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3676" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D3676" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3676" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3676"/>
+  <dimension ref="A1:E3677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99668,6 +99668,33 @@
         </is>
       </c>
     </row>
+    <row r="3677">
+      <c r="A3677" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B3677" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3677" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D3677" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E3677" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3677"/>
+  <dimension ref="A1:E3678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99695,6 +99695,33 @@
         </is>
       </c>
     </row>
+    <row r="3678">
+      <c r="A3678" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B3678" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3678" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3678" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E3678" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3678"/>
+  <dimension ref="A1:E3679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99722,6 +99722,33 @@
         </is>
       </c>
     </row>
+    <row r="3679">
+      <c r="A3679" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B3679" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3679" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3679" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3679" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3679"/>
+  <dimension ref="A1:E3680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99749,6 +99749,33 @@
         </is>
       </c>
     </row>
+    <row r="3680">
+      <c r="A3680" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B3680" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3680" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D3680" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E3680" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3680"/>
+  <dimension ref="A1:E3681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99776,6 +99776,33 @@
         </is>
       </c>
     </row>
+    <row r="3681">
+      <c r="A3681" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B3681" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3681" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3681" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3681" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3681"/>
+  <dimension ref="A1:E3682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99803,6 +99803,33 @@
         </is>
       </c>
     </row>
+    <row r="3682">
+      <c r="A3682" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B3682" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3682" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3682" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E3682" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3682"/>
+  <dimension ref="A1:E3683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99830,6 +99830,33 @@
         </is>
       </c>
     </row>
+    <row r="3683">
+      <c r="A3683" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B3683" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3683" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3683" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3683" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3683"/>
+  <dimension ref="A1:E3684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99857,6 +99857,33 @@
         </is>
       </c>
     </row>
+    <row r="3684">
+      <c r="A3684" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B3684" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3684" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3684" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E3684" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3684"/>
+  <dimension ref="A1:E3685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99884,6 +99884,33 @@
         </is>
       </c>
     </row>
+    <row r="3685">
+      <c r="A3685" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B3685" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3685" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3685" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3685" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3685"/>
+  <dimension ref="A1:E3686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99911,6 +99911,33 @@
         </is>
       </c>
     </row>
+    <row r="3686">
+      <c r="A3686" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B3686" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3686" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D3686" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E3686" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3686"/>
+  <dimension ref="A1:E3687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99938,6 +99938,33 @@
         </is>
       </c>
     </row>
+    <row r="3687">
+      <c r="A3687" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B3687" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3687" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D3687" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E3687" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3687"/>
+  <dimension ref="A1:E3688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99965,6 +99965,33 @@
         </is>
       </c>
     </row>
+    <row r="3688">
+      <c r="A3688" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B3688" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3688" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3688" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3688" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3688"/>
+  <dimension ref="A1:E3689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99992,6 +99992,33 @@
         </is>
       </c>
     </row>
+    <row r="3689">
+      <c r="A3689" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B3689" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3689" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D3689" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E3689" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3689"/>
+  <dimension ref="A1:E3690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100019,6 +100019,33 @@
         </is>
       </c>
     </row>
+    <row r="3690">
+      <c r="A3690" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B3690" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3690" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3690" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3690" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3690"/>
+  <dimension ref="A1:E3691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100046,6 +100046,33 @@
         </is>
       </c>
     </row>
+    <row r="3691">
+      <c r="A3691" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B3691" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3691" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3691" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E3691" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3691"/>
+  <dimension ref="A1:E3692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100073,6 +100073,33 @@
         </is>
       </c>
     </row>
+    <row r="3692">
+      <c r="A3692" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B3692" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3692" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D3692" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3692" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3692"/>
+  <dimension ref="A1:E3693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100100,6 +100100,33 @@
         </is>
       </c>
     </row>
+    <row r="3693">
+      <c r="A3693" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B3693" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3693" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3693" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3693" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3693"/>
+  <dimension ref="A1:E3694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100127,6 +100127,33 @@
         </is>
       </c>
     </row>
+    <row r="3694">
+      <c r="A3694" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B3694" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3694" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3694" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3694" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3694"/>
+  <dimension ref="A1:E3695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100154,6 +100154,33 @@
         </is>
       </c>
     </row>
+    <row r="3695">
+      <c r="A3695" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B3695" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3695" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3695" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3695" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3695"/>
+  <dimension ref="A1:E3696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100181,6 +100181,33 @@
         </is>
       </c>
     </row>
+    <row r="3696">
+      <c r="A3696" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B3696" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3696" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3696" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3696" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3696"/>
+  <dimension ref="A1:E3698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100208,6 +100208,60 @@
         </is>
       </c>
     </row>
+    <row r="3697">
+      <c r="A3697" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B3697" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3697" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3697" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3697" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3698">
+      <c r="A3698" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B3698" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3698" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3698" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3698" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3698"/>
+  <dimension ref="A1:E3699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100262,6 +100262,33 @@
         </is>
       </c>
     </row>
+    <row r="3699">
+      <c r="A3699" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B3699" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3699" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3699" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3699" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3699"/>
+  <dimension ref="A1:E3700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100289,6 +100289,33 @@
         </is>
       </c>
     </row>
+    <row r="3700">
+      <c r="A3700" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B3700" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3700" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3700" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3700" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3700"/>
+  <dimension ref="A1:E3701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100316,6 +100316,33 @@
         </is>
       </c>
     </row>
+    <row r="3701">
+      <c r="A3701" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B3701" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3701" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D3701" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E3701" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3701"/>
+  <dimension ref="A1:E3702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100343,6 +100343,33 @@
         </is>
       </c>
     </row>
+    <row r="3702">
+      <c r="A3702" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B3702" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3702" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D3702" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E3702" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3702"/>
+  <dimension ref="A1:E3703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100370,6 +100370,33 @@
         </is>
       </c>
     </row>
+    <row r="3703">
+      <c r="A3703" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B3703" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3703" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D3703" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E3703" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3703"/>
+  <dimension ref="A1:E3704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100397,6 +100397,33 @@
         </is>
       </c>
     </row>
+    <row r="3704">
+      <c r="A3704" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B3704" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3704" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3704" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E3704" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3704"/>
+  <dimension ref="A1:E3705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100424,6 +100424,33 @@
         </is>
       </c>
     </row>
+    <row r="3705">
+      <c r="A3705" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3705" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3705" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D3705" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E3705" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3705"/>
+  <dimension ref="A1:E3706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100451,6 +100451,33 @@
         </is>
       </c>
     </row>
+    <row r="3706">
+      <c r="A3706" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3706" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3706" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D3706" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3706" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3706"/>
+  <dimension ref="A1:E3707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100478,6 +100478,33 @@
         </is>
       </c>
     </row>
+    <row r="3707">
+      <c r="A3707" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B3707" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3707" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3707" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3707" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3707"/>
+  <dimension ref="A1:E3708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100505,6 +100505,33 @@
         </is>
       </c>
     </row>
+    <row r="3708">
+      <c r="A3708" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B3708" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3708" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D3708" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3708" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3708"/>
+  <dimension ref="A1:E3709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100532,6 +100532,33 @@
         </is>
       </c>
     </row>
+    <row r="3709">
+      <c r="A3709" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B3709" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3709" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3709" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3709" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3709"/>
+  <dimension ref="A1:E3710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100559,6 +100559,33 @@
         </is>
       </c>
     </row>
+    <row r="3710">
+      <c r="A3710" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B3710" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3710" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3710" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3710" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3710"/>
+  <dimension ref="A1:E3711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100586,6 +100586,33 @@
         </is>
       </c>
     </row>
+    <row r="3711">
+      <c r="A3711" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B3711" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3711" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D3711" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E3711" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3711"/>
+  <dimension ref="A1:E3712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100613,6 +100613,33 @@
         </is>
       </c>
     </row>
+    <row r="3712">
+      <c r="A3712" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B3712" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3712" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D3712" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E3712" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3712"/>
+  <dimension ref="A1:E3713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100640,6 +100640,33 @@
         </is>
       </c>
     </row>
+    <row r="3713">
+      <c r="A3713" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B3713" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3713" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3713" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3713" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3713"/>
+  <dimension ref="A1:E3714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100667,6 +100667,33 @@
         </is>
       </c>
     </row>
+    <row r="3714">
+      <c r="A3714" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B3714" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3714" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D3714" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3714" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3714"/>
+  <dimension ref="A1:E3716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100694,6 +100694,60 @@
         </is>
       </c>
     </row>
+    <row r="3715">
+      <c r="A3715" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B3715" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3715" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3715" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E3715" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="3716">
+      <c r="A3716" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B3716" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3716" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D3716" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E3716" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3716"/>
+  <dimension ref="A1:E3717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100748,6 +100748,33 @@
         </is>
       </c>
     </row>
+    <row r="3717">
+      <c r="A3717" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B3717" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3717" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3717" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E3717" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3717"/>
+  <dimension ref="A1:E3718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100775,6 +100775,33 @@
         </is>
       </c>
     </row>
+    <row r="3718">
+      <c r="A3718" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B3718" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3718" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3718" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E3718" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3718"/>
+  <dimension ref="A1:E3719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100802,6 +100802,33 @@
         </is>
       </c>
     </row>
+    <row r="3719">
+      <c r="A3719" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B3719" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3719" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D3719" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E3719" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3719"/>
+  <dimension ref="A1:E3720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100829,6 +100829,33 @@
         </is>
       </c>
     </row>
+    <row r="3720">
+      <c r="A3720" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B3720" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3720" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3720" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E3720" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3720"/>
+  <dimension ref="A1:E3721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100856,6 +100856,33 @@
         </is>
       </c>
     </row>
+    <row r="3721">
+      <c r="A3721" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3721" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3721" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D3721" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3721" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3721"/>
+  <dimension ref="A1:E3722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100883,6 +100883,33 @@
         </is>
       </c>
     </row>
+    <row r="3722">
+      <c r="A3722" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3722" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3722" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3722" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3722" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3722"/>
+  <dimension ref="A1:E3723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100910,6 +100910,33 @@
         </is>
       </c>
     </row>
+    <row r="3723">
+      <c r="A3723" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B3723" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3723" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3723" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E3723" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3723"/>
+  <dimension ref="A1:E3724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100937,6 +100937,33 @@
         </is>
       </c>
     </row>
+    <row r="3724">
+      <c r="A3724" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B3724" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3724" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D3724" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E3724" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3724"/>
+  <dimension ref="A1:E3725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100964,6 +100964,33 @@
         </is>
       </c>
     </row>
+    <row r="3725">
+      <c r="A3725" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B3725" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3725" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D3725" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3725" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3725"/>
+  <dimension ref="A1:E3726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100991,6 +100991,33 @@
         </is>
       </c>
     </row>
+    <row r="3726">
+      <c r="A3726" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B3726" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3726" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D3726" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3726" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3726"/>
+  <dimension ref="A1:E3727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101018,6 +101018,33 @@
         </is>
       </c>
     </row>
+    <row r="3727">
+      <c r="A3727" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B3727" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3727" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D3727" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3727" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3727"/>
+  <dimension ref="A1:E3728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101045,6 +101045,33 @@
         </is>
       </c>
     </row>
+    <row r="3728">
+      <c r="A3728" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B3728" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3728" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D3728" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E3728" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3728"/>
+  <dimension ref="A1:E3729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101072,6 +101072,33 @@
         </is>
       </c>
     </row>
+    <row r="3729">
+      <c r="A3729" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B3729" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3729" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3729" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E3729" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3729"/>
+  <dimension ref="A1:E3730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101099,6 +101099,33 @@
         </is>
       </c>
     </row>
+    <row r="3730">
+      <c r="A3730" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B3730" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3730" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D3730" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3730" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3730"/>
+  <dimension ref="A1:E3731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101126,6 +101126,33 @@
         </is>
       </c>
     </row>
+    <row r="3731">
+      <c r="A3731" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B3731" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3731" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D3731" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3731" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3731"/>
+  <dimension ref="A1:E3732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101153,6 +101153,33 @@
         </is>
       </c>
     </row>
+    <row r="3732">
+      <c r="A3732" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B3732" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3732" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D3732" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3732" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3732"/>
+  <dimension ref="A1:E3733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101180,6 +101180,33 @@
         </is>
       </c>
     </row>
+    <row r="3733">
+      <c r="A3733" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B3733" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3733" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D3733" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E3733" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3733"/>
+  <dimension ref="A1:E3734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101207,6 +101207,33 @@
         </is>
       </c>
     </row>
+    <row r="3734">
+      <c r="A3734" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B3734" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3734" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D3734" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3734" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3734"/>
+  <dimension ref="A1:E3735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101234,6 +101234,33 @@
         </is>
       </c>
     </row>
+    <row r="3735">
+      <c r="A3735" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B3735" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3735" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3735" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3735" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3735"/>
+  <dimension ref="A1:E3736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101261,6 +101261,33 @@
         </is>
       </c>
     </row>
+    <row r="3736">
+      <c r="A3736" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B3736" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3736" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D3736" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3736" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3736"/>
+  <dimension ref="A1:E3737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101288,6 +101288,33 @@
         </is>
       </c>
     </row>
+    <row r="3737">
+      <c r="A3737" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B3737" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3737" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3737" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E3737" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3737"/>
+  <dimension ref="A1:E3738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101315,6 +101315,33 @@
         </is>
       </c>
     </row>
+    <row r="3738">
+      <c r="A3738" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B3738" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3738" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3738" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E3738" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3738"/>
+  <dimension ref="A1:E3739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101342,6 +101342,33 @@
         </is>
       </c>
     </row>
+    <row r="3739">
+      <c r="A3739" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B3739" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3739" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D3739" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3739" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3739"/>
+  <dimension ref="A1:E3740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101369,6 +101369,33 @@
         </is>
       </c>
     </row>
+    <row r="3740">
+      <c r="A3740" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B3740" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3740" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3740" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3740" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3740"/>
+  <dimension ref="A1:E3741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101396,6 +101396,33 @@
         </is>
       </c>
     </row>
+    <row r="3741">
+      <c r="A3741" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B3741" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3741" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3741" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E3741" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3741"/>
+  <dimension ref="A1:E3742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101423,6 +101423,33 @@
         </is>
       </c>
     </row>
+    <row r="3742">
+      <c r="A3742" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B3742" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3742" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3742" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3742" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3742"/>
+  <dimension ref="A1:E3743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101450,6 +101450,33 @@
         </is>
       </c>
     </row>
+    <row r="3743">
+      <c r="A3743" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B3743" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3743" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D3743" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E3743" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3743"/>
+  <dimension ref="A1:E3744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101477,6 +101477,33 @@
         </is>
       </c>
     </row>
+    <row r="3744">
+      <c r="A3744" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B3744" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3744" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D3744" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E3744" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3744"/>
+  <dimension ref="A1:E3745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101504,6 +101504,33 @@
         </is>
       </c>
     </row>
+    <row r="3745">
+      <c r="A3745" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B3745" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3745" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3745" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E3745" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3745"/>
+  <dimension ref="A1:E3746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101531,6 +101531,33 @@
         </is>
       </c>
     </row>
+    <row r="3746">
+      <c r="A3746" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B3746" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3746" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D3746" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3746" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3746"/>
+  <dimension ref="A1:E3747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101558,6 +101558,33 @@
         </is>
       </c>
     </row>
+    <row r="3747">
+      <c r="A3747" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B3747" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3747" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D3747" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E3747" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3747"/>
+  <dimension ref="A1:E3748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101585,6 +101585,33 @@
         </is>
       </c>
     </row>
+    <row r="3748">
+      <c r="A3748" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B3748" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3748" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3748" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E3748" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3748"/>
+  <dimension ref="A1:E3749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101612,6 +101612,33 @@
         </is>
       </c>
     </row>
+    <row r="3749">
+      <c r="A3749" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B3749" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3749" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D3749" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E3749" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La nacional history.xlsx
+++ b/data/histories/La nacional history.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3793"/>
+  <dimension ref="A1:E3794"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -102824,6 +102836,33 @@
       <c r="E3793" t="inlineStr">
         <is>
           <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="3794">
+      <c r="A3794" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3794" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3794" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D3794" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3794" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
